--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4883,10 +4883,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>91819291</v>
+        <v>91819292</v>
       </c>
       <c r="B39" t="n">
-        <v>90647</v>
+        <v>90669</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4899,21 +4899,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4923,10 +4923,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>749674.9615912344</v>
+        <v>749687.2159774679</v>
       </c>
       <c r="R39" t="n">
-        <v>7538022.932911679</v>
+        <v>7538152.057944613</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4995,10 +4995,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>91819292</v>
+        <v>110047489</v>
       </c>
       <c r="B40" t="n">
-        <v>90669</v>
+        <v>90645</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5011,21 +5011,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>749687.2159774679</v>
+        <v>749816.9234223666</v>
       </c>
       <c r="R40" t="n">
-        <v>7538152.057944613</v>
+        <v>7538237.456334162</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5095,7 +5095,7 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -5107,10 +5107,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>110047489</v>
+        <v>110047497</v>
       </c>
       <c r="B41" t="n">
-        <v>90645</v>
+        <v>88019</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5119,25 +5119,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>749816.9234223666</v>
+        <v>749807.801174833</v>
       </c>
       <c r="R41" t="n">
-        <v>7538237.456334162</v>
+        <v>7538233.539382952</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5219,10 +5219,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>110047497</v>
+        <v>110047491</v>
       </c>
       <c r="B42" t="n">
-        <v>88019</v>
+        <v>90647</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>749807.801174833</v>
+        <v>749804.775457286</v>
       </c>
       <c r="R42" t="n">
-        <v>7538233.539382952</v>
+        <v>7538229.451174593</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>110047491</v>
+        <v>110050051</v>
       </c>
       <c r="B43" t="n">
-        <v>90647</v>
+        <v>90699</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5343,25 +5343,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>232140</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>749804.775457286</v>
+        <v>749719.4614537557</v>
       </c>
       <c r="R43" t="n">
-        <v>7538229.451174593</v>
+        <v>7538180.223133828</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>110050051</v>
+        <v>110047495</v>
       </c>
       <c r="B44" t="n">
-        <v>90699</v>
+        <v>90641</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>232140</v>
+        <v>149</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>749719.4614537557</v>
+        <v>749818.9873157886</v>
       </c>
       <c r="R44" t="n">
-        <v>7538180.223133828</v>
+        <v>7538235.757213106</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -5555,10 +5555,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>110047495</v>
+        <v>110050046</v>
       </c>
       <c r="B45" t="n">
-        <v>90641</v>
+        <v>90645</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5567,25 +5567,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>749818.9873157886</v>
+        <v>749732.6391948935</v>
       </c>
       <c r="R45" t="n">
-        <v>7538235.757213106</v>
+        <v>7538181.493667146</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -5667,10 +5667,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>110050046</v>
+        <v>110047477</v>
       </c>
       <c r="B46" t="n">
-        <v>90645</v>
+        <v>90647</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5683,21 +5683,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>749732.6391948935</v>
+        <v>749853.8156241401</v>
       </c>
       <c r="R46" t="n">
-        <v>7538181.493667146</v>
+        <v>7538229.246132255</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -5779,7 +5779,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>110047477</v>
+        <v>110047471</v>
       </c>
       <c r="B47" t="n">
         <v>90647</v>
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>749853.8156241401</v>
+        <v>749830.1972224362</v>
       </c>
       <c r="R47" t="n">
-        <v>7538229.246132255</v>
+        <v>7538296.820639784</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5891,7 +5891,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>110047471</v>
+        <v>110047472</v>
       </c>
       <c r="B48" t="n">
         <v>90647</v>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>749830.1972224362</v>
+        <v>749858.5469831147</v>
       </c>
       <c r="R48" t="n">
-        <v>7538296.820639784</v>
+        <v>7538247.165943973</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6003,7 +6003,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>110047472</v>
+        <v>110050030</v>
       </c>
       <c r="B49" t="n">
         <v>90647</v>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>749858.5469831147</v>
+        <v>749715.582271572</v>
       </c>
       <c r="R49" t="n">
-        <v>7538247.165943973</v>
+        <v>7538169.219110462</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -6115,7 +6115,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>110050030</v>
+        <v>110047486</v>
       </c>
       <c r="B50" t="n">
         <v>90647</v>
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>749715.582271572</v>
+        <v>749792.5059387208</v>
       </c>
       <c r="R50" t="n">
-        <v>7538169.219110462</v>
+        <v>7538250.286772298</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -6227,10 +6227,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>110047486</v>
+        <v>110047498</v>
       </c>
       <c r="B51" t="n">
-        <v>90647</v>
+        <v>88019</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6239,25 +6239,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>749792.5059387208</v>
+        <v>749782.7395398659</v>
       </c>
       <c r="R51" t="n">
-        <v>7538250.286772298</v>
+        <v>7538245.168893935</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6339,10 +6339,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>110047498</v>
+        <v>110050034</v>
       </c>
       <c r="B52" t="n">
-        <v>88019</v>
+        <v>90657</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>749782.7395398659</v>
+        <v>749719.4614537557</v>
       </c>
       <c r="R52" t="n">
-        <v>7538245.168893935</v>
+        <v>7538180.223133828</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -6451,10 +6451,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>110050034</v>
+        <v>110050048</v>
       </c>
       <c r="B53" t="n">
-        <v>90657</v>
+        <v>89633</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6467,21 +6467,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4365</v>
+        <v>65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>749719.4614537557</v>
+        <v>749711.680657233</v>
       </c>
       <c r="R53" t="n">
-        <v>7538180.223133828</v>
+        <v>7538162.388993432</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6563,10 +6563,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>110050048</v>
+        <v>110050035</v>
       </c>
       <c r="B54" t="n">
-        <v>89633</v>
+        <v>88476</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6575,25 +6575,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>749711.680657233</v>
+        <v>749723.6168781928</v>
       </c>
       <c r="R54" t="n">
-        <v>7538162.388993432</v>
+        <v>7538184.420200526</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6675,10 +6675,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>110050035</v>
+        <v>110047499</v>
       </c>
       <c r="B55" t="n">
-        <v>88476</v>
+        <v>90647</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6691,21 +6691,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>749723.6168781928</v>
+        <v>749779.7050400365</v>
       </c>
       <c r="R55" t="n">
-        <v>7538184.420200526</v>
+        <v>7538249.052237583</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -6784,118 +6784,6 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>110047499</v>
-      </c>
-      <c r="B56" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Esrangeåsen, T lm</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>749779.7050400365</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7538249.052237583</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Robert Sandberg</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6785,6 +6785,1170 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128691463</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>749698</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7538155</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128691423</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91386</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>749677</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7538134</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128691457</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>749701</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7538166</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128691459</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>749749</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7538214</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128691440</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92790</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>749833</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7538296</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128691455</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91725</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>65</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>749707</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7538174</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128691422</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91386</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>749652</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7538048</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128691456</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>749799</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7538192</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128691462</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>749676</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7538135</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128691425</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>749710</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7538102</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128691438</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92746</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>749709</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7538091</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128691461</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>749702</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7538089</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6787,10 +6787,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128691463</v>
+        <v>128691423</v>
       </c>
       <c r="B56" t="n">
-        <v>92748</v>
+        <v>91388</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>749698</v>
+        <v>749677</v>
       </c>
       <c r="R56" t="n">
-        <v>7538155</v>
+        <v>7538134</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128691423</v>
+        <v>128691463</v>
       </c>
       <c r="B57" t="n">
-        <v>91386</v>
+        <v>92750</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>749677</v>
+        <v>749698</v>
       </c>
       <c r="R57" t="n">
-        <v>7538134</v>
+        <v>7538155</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
         <v>128691457</v>
       </c>
       <c r="B58" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>128691459</v>
       </c>
       <c r="B59" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,32 +7175,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691440</v>
+        <v>128691455</v>
       </c>
       <c r="B60" t="n">
-        <v>92790</v>
+        <v>91727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749833</v>
+        <v>749707</v>
       </c>
       <c r="R60" t="n">
-        <v>7538296</v>
+        <v>7538174</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,32 +7272,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691455</v>
+        <v>128691440</v>
       </c>
       <c r="B61" t="n">
-        <v>91725</v>
+        <v>92792</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749707</v>
+        <v>749833</v>
       </c>
       <c r="R61" t="n">
-        <v>7538174</v>
+        <v>7538296</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
         <v>128691422</v>
       </c>
       <c r="B62" t="n">
-        <v>91386</v>
+        <v>91388</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128691456</v>
       </c>
       <c r="B63" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>128691462</v>
       </c>
       <c r="B64" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>128691425</v>
       </c>
       <c r="B65" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>128691438</v>
       </c>
       <c r="B66" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>128691461</v>
       </c>
       <c r="B67" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6787,10 +6787,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128691423</v>
+        <v>128691463</v>
       </c>
       <c r="B56" t="n">
-        <v>91388</v>
+        <v>92750</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>749677</v>
+        <v>749698</v>
       </c>
       <c r="R56" t="n">
-        <v>7538134</v>
+        <v>7538155</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128691463</v>
+        <v>128691423</v>
       </c>
       <c r="B57" t="n">
-        <v>92750</v>
+        <v>91388</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>749698</v>
+        <v>749677</v>
       </c>
       <c r="R57" t="n">
-        <v>7538155</v>
+        <v>7538134</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6790,7 +6790,7 @@
         <v>128691463</v>
       </c>
       <c r="B56" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>128691423</v>
       </c>
       <c r="B57" t="n">
-        <v>91388</v>
+        <v>91389</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>128691457</v>
       </c>
       <c r="B58" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>128691459</v>
       </c>
       <c r="B59" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>128691455</v>
       </c>
       <c r="B60" t="n">
-        <v>91727</v>
+        <v>91728</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>128691440</v>
       </c>
       <c r="B61" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>128691422</v>
       </c>
       <c r="B62" t="n">
-        <v>91388</v>
+        <v>91389</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128691456</v>
       </c>
       <c r="B63" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>128691462</v>
       </c>
       <c r="B64" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>128691438</v>
       </c>
       <c r="B66" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>128691461</v>
       </c>
       <c r="B67" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6790,7 +6790,7 @@
         <v>128691463</v>
       </c>
       <c r="B56" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>128691423</v>
       </c>
       <c r="B57" t="n">
-        <v>91389</v>
+        <v>91416</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>128691457</v>
       </c>
       <c r="B58" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>128691459</v>
       </c>
       <c r="B59" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>128691455</v>
       </c>
       <c r="B60" t="n">
-        <v>91728</v>
+        <v>91755</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>128691440</v>
       </c>
       <c r="B61" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>128691422</v>
       </c>
       <c r="B62" t="n">
-        <v>91389</v>
+        <v>91416</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128691456</v>
       </c>
       <c r="B63" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>128691462</v>
       </c>
       <c r="B64" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>128691425</v>
       </c>
       <c r="B65" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>128691438</v>
       </c>
       <c r="B66" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>128691461</v>
       </c>
       <c r="B67" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -7175,32 +7175,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691455</v>
+        <v>128691440</v>
       </c>
       <c r="B60" t="n">
-        <v>91755</v>
+        <v>92820</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749707</v>
+        <v>749833</v>
       </c>
       <c r="R60" t="n">
-        <v>7538174</v>
+        <v>7538296</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,32 +7272,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691440</v>
+        <v>128691455</v>
       </c>
       <c r="B61" t="n">
-        <v>92820</v>
+        <v>91755</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749833</v>
+        <v>749707</v>
       </c>
       <c r="R61" t="n">
-        <v>7538296</v>
+        <v>7538174</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6790,7 +6790,7 @@
         <v>128691463</v>
       </c>
       <c r="B56" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>128691423</v>
       </c>
       <c r="B57" t="n">
-        <v>91416</v>
+        <v>91421</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>128691457</v>
       </c>
       <c r="B58" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>128691459</v>
       </c>
       <c r="B59" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,32 +7175,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691440</v>
+        <v>128691455</v>
       </c>
       <c r="B60" t="n">
-        <v>92820</v>
+        <v>91760</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749833</v>
+        <v>749707</v>
       </c>
       <c r="R60" t="n">
-        <v>7538296</v>
+        <v>7538174</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,32 +7272,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691455</v>
+        <v>128691440</v>
       </c>
       <c r="B61" t="n">
-        <v>91755</v>
+        <v>92825</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749707</v>
+        <v>749833</v>
       </c>
       <c r="R61" t="n">
-        <v>7538174</v>
+        <v>7538296</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
         <v>128691422</v>
       </c>
       <c r="B62" t="n">
-        <v>91416</v>
+        <v>91421</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128691456</v>
       </c>
       <c r="B63" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>128691462</v>
       </c>
       <c r="B64" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>128691425</v>
       </c>
       <c r="B65" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>128691438</v>
       </c>
       <c r="B66" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>128691461</v>
       </c>
       <c r="B67" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6787,10 +6787,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128691463</v>
+        <v>128691423</v>
       </c>
       <c r="B56" t="n">
-        <v>92783</v>
+        <v>91426</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>749698</v>
+        <v>749677</v>
       </c>
       <c r="R56" t="n">
-        <v>7538155</v>
+        <v>7538134</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128691423</v>
+        <v>128691463</v>
       </c>
       <c r="B57" t="n">
-        <v>91421</v>
+        <v>92788</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>749677</v>
+        <v>749698</v>
       </c>
       <c r="R57" t="n">
-        <v>7538134</v>
+        <v>7538155</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
         <v>128691457</v>
       </c>
       <c r="B58" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>128691459</v>
       </c>
       <c r="B59" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,32 +7175,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691455</v>
+        <v>128691440</v>
       </c>
       <c r="B60" t="n">
-        <v>91760</v>
+        <v>92832</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749707</v>
+        <v>749833</v>
       </c>
       <c r="R60" t="n">
-        <v>7538174</v>
+        <v>7538296</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,32 +7272,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691440</v>
+        <v>128691455</v>
       </c>
       <c r="B61" t="n">
-        <v>92825</v>
+        <v>91765</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749833</v>
+        <v>749707</v>
       </c>
       <c r="R61" t="n">
-        <v>7538296</v>
+        <v>7538174</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
         <v>128691422</v>
       </c>
       <c r="B62" t="n">
-        <v>91421</v>
+        <v>91426</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128691456</v>
       </c>
       <c r="B63" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>128691462</v>
       </c>
       <c r="B64" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>128691438</v>
       </c>
       <c r="B66" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>128691461</v>
       </c>
       <c r="B67" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6787,10 +6787,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128691423</v>
+        <v>128691463</v>
       </c>
       <c r="B56" t="n">
-        <v>91426</v>
+        <v>92788</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>749677</v>
+        <v>749698</v>
       </c>
       <c r="R56" t="n">
-        <v>7538134</v>
+        <v>7538155</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128691463</v>
+        <v>128691423</v>
       </c>
       <c r="B57" t="n">
-        <v>92788</v>
+        <v>91426</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>749698</v>
+        <v>749677</v>
       </c>
       <c r="R57" t="n">
-        <v>7538155</v>
+        <v>7538134</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6787,10 +6787,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128691463</v>
+        <v>128691423</v>
       </c>
       <c r="B56" t="n">
-        <v>92788</v>
+        <v>91426</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>749698</v>
+        <v>749677</v>
       </c>
       <c r="R56" t="n">
-        <v>7538155</v>
+        <v>7538134</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128691423</v>
+        <v>128691463</v>
       </c>
       <c r="B57" t="n">
-        <v>91426</v>
+        <v>92788</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>749677</v>
+        <v>749698</v>
       </c>
       <c r="R57" t="n">
-        <v>7538134</v>
+        <v>7538155</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7175,32 +7175,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691440</v>
+        <v>128691455</v>
       </c>
       <c r="B60" t="n">
-        <v>92832</v>
+        <v>91765</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749833</v>
+        <v>749707</v>
       </c>
       <c r="R60" t="n">
-        <v>7538296</v>
+        <v>7538174</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,32 +7272,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691455</v>
+        <v>128691440</v>
       </c>
       <c r="B61" t="n">
-        <v>91765</v>
+        <v>92832</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749707</v>
+        <v>749833</v>
       </c>
       <c r="R61" t="n">
-        <v>7538174</v>
+        <v>7538296</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6790,7 +6790,7 @@
         <v>128691423</v>
       </c>
       <c r="B56" t="n">
-        <v>91426</v>
+        <v>91430</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>128691463</v>
       </c>
       <c r="B57" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>128691457</v>
       </c>
       <c r="B58" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>128691459</v>
       </c>
       <c r="B59" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,32 +7175,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691455</v>
+        <v>128691440</v>
       </c>
       <c r="B60" t="n">
-        <v>91765</v>
+        <v>92836</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749707</v>
+        <v>749833</v>
       </c>
       <c r="R60" t="n">
-        <v>7538174</v>
+        <v>7538296</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,32 +7272,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691440</v>
+        <v>128691455</v>
       </c>
       <c r="B61" t="n">
-        <v>92832</v>
+        <v>91769</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749833</v>
+        <v>749707</v>
       </c>
       <c r="R61" t="n">
-        <v>7538296</v>
+        <v>7538174</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
         <v>128691422</v>
       </c>
       <c r="B62" t="n">
-        <v>91426</v>
+        <v>91430</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128691456</v>
       </c>
       <c r="B63" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>128691462</v>
       </c>
       <c r="B64" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>128691425</v>
       </c>
       <c r="B65" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>128691438</v>
       </c>
       <c r="B66" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>128691461</v>
       </c>
       <c r="B67" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -7175,32 +7175,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691440</v>
+        <v>128691455</v>
       </c>
       <c r="B60" t="n">
-        <v>92836</v>
+        <v>91769</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749833</v>
+        <v>749707</v>
       </c>
       <c r="R60" t="n">
-        <v>7538296</v>
+        <v>7538174</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,32 +7272,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691455</v>
+        <v>128691440</v>
       </c>
       <c r="B61" t="n">
-        <v>91769</v>
+        <v>92836</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749707</v>
+        <v>749833</v>
       </c>
       <c r="R61" t="n">
-        <v>7538174</v>
+        <v>7538296</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6787,10 +6787,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128691423</v>
+        <v>128691463</v>
       </c>
       <c r="B56" t="n">
-        <v>91430</v>
+        <v>92797</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>749677</v>
+        <v>749698</v>
       </c>
       <c r="R56" t="n">
-        <v>7538134</v>
+        <v>7538155</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128691463</v>
+        <v>128691423</v>
       </c>
       <c r="B57" t="n">
-        <v>92792</v>
+        <v>91435</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>749698</v>
+        <v>749677</v>
       </c>
       <c r="R57" t="n">
-        <v>7538155</v>
+        <v>7538134</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
         <v>128691457</v>
       </c>
       <c r="B58" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>128691459</v>
       </c>
       <c r="B59" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,32 +7175,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691455</v>
+        <v>128691440</v>
       </c>
       <c r="B60" t="n">
-        <v>91769</v>
+        <v>92841</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749707</v>
+        <v>749833</v>
       </c>
       <c r="R60" t="n">
-        <v>7538174</v>
+        <v>7538296</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,32 +7272,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691440</v>
+        <v>128691455</v>
       </c>
       <c r="B61" t="n">
-        <v>92836</v>
+        <v>91774</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749833</v>
+        <v>749707</v>
       </c>
       <c r="R61" t="n">
-        <v>7538296</v>
+        <v>7538174</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
         <v>128691422</v>
       </c>
       <c r="B62" t="n">
-        <v>91430</v>
+        <v>91435</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128691456</v>
       </c>
       <c r="B63" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>128691462</v>
       </c>
       <c r="B64" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>128691425</v>
       </c>
       <c r="B65" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>128691438</v>
       </c>
       <c r="B66" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>128691461</v>
       </c>
       <c r="B67" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6790,7 +6790,7 @@
         <v>128691423</v>
       </c>
       <c r="B56" t="n">
-        <v>91442</v>
+        <v>91445</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>128691463</v>
       </c>
       <c r="B57" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>128691457</v>
       </c>
       <c r="B58" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>128691459</v>
       </c>
       <c r="B59" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>128691455</v>
       </c>
       <c r="B60" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>128691440</v>
       </c>
       <c r="B61" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>128691422</v>
       </c>
       <c r="B62" t="n">
-        <v>91442</v>
+        <v>91445</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128691456</v>
       </c>
       <c r="B63" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>128691462</v>
       </c>
       <c r="B64" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>128691438</v>
       </c>
       <c r="B66" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>128691461</v>
       </c>
       <c r="B67" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6790,7 +6790,7 @@
         <v>128691423</v>
       </c>
       <c r="B56" t="n">
-        <v>91445</v>
+        <v>91448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>128691463</v>
       </c>
       <c r="B57" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>128691457</v>
       </c>
       <c r="B58" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>128691459</v>
       </c>
       <c r="B59" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>128691455</v>
       </c>
       <c r="B60" t="n">
-        <v>91784</v>
+        <v>91787</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>128691440</v>
       </c>
       <c r="B61" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>128691422</v>
       </c>
       <c r="B62" t="n">
-        <v>91445</v>
+        <v>91448</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128691456</v>
       </c>
       <c r="B63" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>128691462</v>
       </c>
       <c r="B64" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>128691425</v>
       </c>
       <c r="B65" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>128691438</v>
       </c>
       <c r="B66" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>128691461</v>
       </c>
       <c r="B67" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6787,10 +6787,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128691423</v>
+        <v>128691463</v>
       </c>
       <c r="B56" t="n">
-        <v>91448</v>
+        <v>92813</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>749677</v>
+        <v>749698</v>
       </c>
       <c r="R56" t="n">
-        <v>7538134</v>
+        <v>7538155</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128691463</v>
+        <v>128691423</v>
       </c>
       <c r="B57" t="n">
-        <v>92813</v>
+        <v>91448</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>749698</v>
+        <v>749677</v>
       </c>
       <c r="R57" t="n">
-        <v>7538155</v>
+        <v>7538134</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7175,32 +7175,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691455</v>
+        <v>128691440</v>
       </c>
       <c r="B60" t="n">
-        <v>91787</v>
+        <v>92857</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749707</v>
+        <v>749833</v>
       </c>
       <c r="R60" t="n">
-        <v>7538174</v>
+        <v>7538296</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,32 +7272,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691440</v>
+        <v>128691455</v>
       </c>
       <c r="B61" t="n">
-        <v>92857</v>
+        <v>91787</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749833</v>
+        <v>749707</v>
       </c>
       <c r="R61" t="n">
-        <v>7538296</v>
+        <v>7538174</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6787,10 +6787,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128691463</v>
+        <v>128691423</v>
       </c>
       <c r="B56" t="n">
-        <v>92813</v>
+        <v>91448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>749698</v>
+        <v>749677</v>
       </c>
       <c r="R56" t="n">
-        <v>7538155</v>
+        <v>7538134</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128691423</v>
+        <v>128691463</v>
       </c>
       <c r="B57" t="n">
-        <v>91448</v>
+        <v>92813</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>749677</v>
+        <v>749698</v>
       </c>
       <c r="R57" t="n">
-        <v>7538134</v>
+        <v>7538155</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7175,32 +7175,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691440</v>
+        <v>128691455</v>
       </c>
       <c r="B60" t="n">
-        <v>92857</v>
+        <v>91787</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749833</v>
+        <v>749707</v>
       </c>
       <c r="R60" t="n">
-        <v>7538296</v>
+        <v>7538174</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,32 +7272,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691455</v>
+        <v>128691440</v>
       </c>
       <c r="B61" t="n">
-        <v>91787</v>
+        <v>92857</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749707</v>
+        <v>749833</v>
       </c>
       <c r="R61" t="n">
-        <v>7538174</v>
+        <v>7538296</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -6787,10 +6787,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128691423</v>
+        <v>128691463</v>
       </c>
       <c r="B56" t="n">
-        <v>91448</v>
+        <v>92820</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>749677</v>
+        <v>749698</v>
       </c>
       <c r="R56" t="n">
-        <v>7538134</v>
+        <v>7538155</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128691463</v>
+        <v>128691423</v>
       </c>
       <c r="B57" t="n">
-        <v>92813</v>
+        <v>91454</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>749698</v>
+        <v>749677</v>
       </c>
       <c r="R57" t="n">
-        <v>7538155</v>
+        <v>7538134</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6984,7 +6984,7 @@
         <v>128691457</v>
       </c>
       <c r="B58" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>128691459</v>
       </c>
       <c r="B59" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,32 +7175,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691455</v>
+        <v>128691440</v>
       </c>
       <c r="B60" t="n">
-        <v>91787</v>
+        <v>92864</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749707</v>
+        <v>749833</v>
       </c>
       <c r="R60" t="n">
-        <v>7538174</v>
+        <v>7538296</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,32 +7272,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691440</v>
+        <v>128691455</v>
       </c>
       <c r="B61" t="n">
-        <v>92857</v>
+        <v>91794</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749833</v>
+        <v>749707</v>
       </c>
       <c r="R61" t="n">
-        <v>7538296</v>
+        <v>7538174</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
         <v>128691422</v>
       </c>
       <c r="B62" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128691456</v>
       </c>
       <c r="B63" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>128691462</v>
       </c>
       <c r="B64" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>128691425</v>
       </c>
       <c r="B65" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>128691438</v>
       </c>
       <c r="B66" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>128691461</v>
       </c>
       <c r="B67" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79797210</v>
+        <v>79797228</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749680.9078443616</v>
+        <v>749715</v>
       </c>
       <c r="R2" t="n">
-        <v>7538063.75018113</v>
+        <v>7538164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2019-09-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79797228</v>
+        <v>80979854</v>
       </c>
       <c r="B3" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,19 +805,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Esrange, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749714.9241846921</v>
+        <v>749718</v>
       </c>
       <c r="R3" t="n">
-        <v>7538164.220281148</v>
+        <v>7538170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,14 +855,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -907,53 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79931285</v>
+        <v>110050048</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Esrangeåsen salmijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749694.9275043921</v>
+        <v>749712</v>
       </c>
       <c r="R4" t="n">
-        <v>7538150.903106983</v>
+        <v>7538162</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,14 +952,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1023,53 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79931265</v>
+        <v>128691455</v>
       </c>
       <c r="B5" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Esrangeåsen salmijärvi, T lm</t>
+          <t>Saarijärvi, T lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749699.1863966796</v>
+        <v>749707</v>
       </c>
       <c r="R5" t="n">
-        <v>7538142.202142274</v>
+        <v>7538174</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,22 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,34 +1049,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79931237</v>
+        <v>79931103</v>
       </c>
       <c r="B6" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>149</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>749719.7515758905</v>
+        <v>749816</v>
       </c>
       <c r="R6" t="n">
-        <v>7538177.213959198</v>
+        <v>7538249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,19 +1138,9 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79931103</v>
+        <v>79931201</v>
       </c>
       <c r="B7" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>749815.7624792359</v>
+        <v>749687</v>
       </c>
       <c r="R7" t="n">
-        <v>7538249.492739198</v>
+        <v>7538163</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,19 +1239,9 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79931201</v>
+        <v>80979847</v>
       </c>
       <c r="B8" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,19 +1298,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Esrangeåsen salmijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>749686.9174436458</v>
+        <v>749810</v>
       </c>
       <c r="R8" t="n">
-        <v>7538163.038879991</v>
+        <v>7538237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,35 +1337,24 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1487,53 +1366,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79931213</v>
+        <v>80979848</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Esrangeåsen salmijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>749686.9174436458</v>
+        <v>749685</v>
       </c>
       <c r="R9" t="n">
-        <v>7538163.038879991</v>
+        <v>7538164</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,35 +1434,24 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1603,53 +1463,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79931308</v>
+        <v>91819293</v>
       </c>
       <c r="B10" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5448</v>
+        <v>149</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Esrangeåsen salmijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>749723.3267514311</v>
+        <v>749834</v>
       </c>
       <c r="R10" t="n">
-        <v>7538187.429366862</v>
+        <v>7538312</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,22 +1528,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,14 +1542,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1719,53 +1560,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>79931292</v>
+        <v>91819301</v>
       </c>
       <c r="B11" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Esrangeåsen salmijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>749670.925623805</v>
+        <v>749690</v>
       </c>
       <c r="R11" t="n">
-        <v>7538143.653990834</v>
+        <v>7538156</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,22 +1625,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,14 +1639,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -1835,53 +1657,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79931078</v>
+        <v>110047495</v>
       </c>
       <c r="B12" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Esrangeåsen salmijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>749853.2853301535</v>
+        <v>749819</v>
       </c>
       <c r="R12" t="n">
-        <v>7538270.195787434</v>
+        <v>7538236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,22 +1722,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,14 +1736,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1951,37 +1754,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>79931208</v>
+        <v>79931255</v>
       </c>
       <c r="B13" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3100</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>749686.9174436458</v>
+        <v>749728</v>
       </c>
       <c r="R13" t="n">
-        <v>7538163.038879991</v>
+        <v>7538148</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2027,19 +1825,9 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,53 +1855,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>79931274</v>
+        <v>80979853</v>
       </c>
       <c r="B14" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Esrangeåsen salmijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>749650.5547619738</v>
+        <v>749726</v>
       </c>
       <c r="R14" t="n">
-        <v>7538110.55928564</v>
+        <v>7538151</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,35 +1923,24 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2183,15 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>79931166</v>
+        <v>110050035</v>
       </c>
       <c r="B15" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,37 +1963,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Esrangeåsen salmijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>749720.5131478321</v>
+        <v>749724</v>
       </c>
       <c r="R15" t="n">
-        <v>7538169.314859165</v>
+        <v>7538185</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,22 +2017,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,14 +2031,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -2299,37 +2049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>79931186</v>
+        <v>79931067</v>
       </c>
       <c r="B16" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2342,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>749674.512544774</v>
+        <v>749856</v>
       </c>
       <c r="R16" t="n">
-        <v>7538023.648957086</v>
+        <v>7538286</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,19 +2120,9 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,15 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>79931255</v>
+        <v>80979851</v>
       </c>
       <c r="B17" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,37 +2161,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Esrangeåsen salmijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>749727.8514445142</v>
+        <v>749855</v>
       </c>
       <c r="R17" t="n">
-        <v>7538148.3825339</v>
+        <v>7538283</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2491,35 +2218,24 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2531,15 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80979854</v>
+        <v>91819292</v>
       </c>
       <c r="B18" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2571,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>749718.1815663308</v>
+        <v>749687</v>
       </c>
       <c r="R18" t="n">
-        <v>7538169.849355761</v>
+        <v>7538152</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,22 +2312,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,37 +2344,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80979860</v>
+        <v>91819295</v>
       </c>
       <c r="B19" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2683,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>749666.0225828955</v>
+        <v>749701</v>
       </c>
       <c r="R19" t="n">
-        <v>7538151.15394965</v>
+        <v>7538158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,22 +2409,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,15 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>80979864</v>
+        <v>79931048</v>
       </c>
       <c r="B20" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2771,34 +2452,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Esrangeåsen salmijärvi, T lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>749733.9018009391</v>
+        <v>749855</v>
       </c>
       <c r="R20" t="n">
-        <v>7538207.810661365</v>
+        <v>7538293</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2828,34 +2512,25 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2867,50 +2542,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80979855</v>
+        <v>79931078</v>
       </c>
       <c r="B21" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Esrangeåsen salmijärvi, T lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>749691.9015150943</v>
+        <v>749853</v>
       </c>
       <c r="R21" t="n">
-        <v>7538146.814930802</v>
+        <v>7538270</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2940,34 +2613,25 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2979,15 +2643,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>80979844</v>
+        <v>79931208</v>
       </c>
       <c r="B22" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,25 +2663,28 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Esrangeåsen salmijärvi, T lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>749694.9915547316</v>
+        <v>749687</v>
       </c>
       <c r="R22" t="n">
-        <v>7538158.122555103</v>
+        <v>7538163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3052,34 +2714,25 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3091,37 +2744,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>80979847</v>
+        <v>80979844</v>
       </c>
       <c r="B23" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3131,10 +2779,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>749810.1101634853</v>
+        <v>749695</v>
       </c>
       <c r="R23" t="n">
-        <v>7538237.178824256</v>
+        <v>7538158</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3164,19 +2812,9 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3203,37 +2841,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>80979853</v>
+        <v>80979845</v>
       </c>
       <c r="B24" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>3100</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3243,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>749726.0915348928</v>
+        <v>749860</v>
       </c>
       <c r="R24" t="n">
-        <v>7538150.870387293</v>
+        <v>7538278</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3276,19 +2909,9 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,37 +2938,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>80979848</v>
+        <v>80979846</v>
       </c>
       <c r="B25" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3355,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>749684.9261160335</v>
+        <v>749848</v>
       </c>
       <c r="R25" t="n">
-        <v>7538163.985851485</v>
+        <v>7538293</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3388,19 +3006,9 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3427,15 +3035,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>80979857</v>
+        <v>91819298</v>
       </c>
       <c r="B26" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3443,21 +3046,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3467,10 +3070,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>749680.0015140411</v>
+        <v>749687</v>
       </c>
       <c r="R26" t="n">
-        <v>7538021.900049888</v>
+        <v>7538152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3497,22 +3100,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,50 +3132,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>80979856</v>
+        <v>128691422</v>
       </c>
       <c r="B27" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Saarijärvi, T lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>749685.0209889594</v>
+        <v>749652</v>
       </c>
       <c r="R27" t="n">
-        <v>7538159.059616382</v>
+        <v>7538048</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3609,22 +3197,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,27 +3217,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>80979858</v>
+        <v>128691423</v>
       </c>
       <c r="B28" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3667,34 +3240,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Saarijärvi, T lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>749718.072771233</v>
+        <v>749677</v>
       </c>
       <c r="R28" t="n">
-        <v>7538170.977799851</v>
+        <v>7538134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3721,22 +3294,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3751,27 +3314,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>80979840</v>
+        <v>110047489</v>
       </c>
       <c r="B29" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3779,21 +3337,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3803,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>749766.1722252226</v>
+        <v>749817</v>
       </c>
       <c r="R29" t="n">
-        <v>7538212.061276111</v>
+        <v>7538238</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3833,22 +3391,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3863,7 +3411,7 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -3875,15 +3423,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>80979863</v>
+        <v>110050046</v>
       </c>
       <c r="B30" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3891,21 +3434,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3915,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>749697.1001554739</v>
+        <v>749733</v>
       </c>
       <c r="R30" t="n">
-        <v>7538148.075381428</v>
+        <v>7538182</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3945,22 +3488,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3975,7 +3508,7 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -3987,15 +3520,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>80979849</v>
+        <v>128691438</v>
       </c>
       <c r="B31" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,34 +3531,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Saarijärvi, T lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>749717.9692822058</v>
+        <v>749709</v>
       </c>
       <c r="R31" t="n">
-        <v>7538183.875697601</v>
+        <v>7538091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4057,22 +3585,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4087,27 +3605,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>80979842</v>
+        <v>79797210</v>
       </c>
       <c r="B32" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4133,16 +3646,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Esrange, T lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>749797.0758331177</v>
+        <v>749681</v>
       </c>
       <c r="R32" t="n">
-        <v>7538317.162856651</v>
+        <v>7538064</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4169,22 +3685,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4193,13 +3699,14 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -4211,50 +3718,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>80979850</v>
+        <v>79930988</v>
       </c>
       <c r="B33" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Esrangeåsen salmijärvi, T lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>749718.0418122963</v>
+        <v>749840</v>
       </c>
       <c r="R33" t="n">
-        <v>7538183.123405341</v>
+        <v>7538303</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4284,34 +3789,25 @@
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2019-09-14</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -4323,15 +3819,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>91819294</v>
+        <v>79930997</v>
       </c>
       <c r="B34" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4357,16 +3848,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Esrangeåsen salmijärvi, T lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>749762.0771391152</v>
+        <v>749850</v>
       </c>
       <c r="R34" t="n">
-        <v>7538234.824310247</v>
+        <v>7538300</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4393,22 +3887,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4417,13 +3901,14 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -4435,50 +3920,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>91819301</v>
+        <v>79931166</v>
       </c>
       <c r="B35" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Esrangeåsen salmijärvi, T lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>749689.8654560882</v>
+        <v>749721</v>
       </c>
       <c r="R35" t="n">
-        <v>7538156.109811397</v>
+        <v>7538169</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,22 +3988,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4529,13 +4002,14 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4547,15 +4021,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>91819298</v>
+        <v>79931186</v>
       </c>
       <c r="B36" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,34 +4032,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Esrangeåsen salmijärvi, T lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>749687.2159774679</v>
+        <v>749675</v>
       </c>
       <c r="R36" t="n">
-        <v>7538152.057944613</v>
+        <v>7538024</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4617,22 +4089,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4641,13 +4103,14 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4659,15 +4122,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>91819299</v>
+        <v>79931265</v>
       </c>
       <c r="B37" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4693,16 +4151,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Esrangeåsen salmijärvi, T lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>749687.2159774679</v>
+        <v>749699</v>
       </c>
       <c r="R37" t="n">
-        <v>7538152.057944613</v>
+        <v>7538142</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4729,22 +4190,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4753,13 +4204,14 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -4771,15 +4223,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>91819295</v>
+        <v>79931274</v>
       </c>
       <c r="B38" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4787,34 +4234,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Esrangeåsen salmijärvi, T lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>749701.0882412114</v>
+        <v>749651</v>
       </c>
       <c r="R38" t="n">
-        <v>7538157.951004753</v>
+        <v>7538111</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4841,22 +4291,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4865,13 +4305,14 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -4883,15 +4324,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>91819292</v>
+        <v>79931292</v>
       </c>
       <c r="B39" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4899,34 +4335,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Esrangeåsen, T lm</t>
+          <t>Esrangeåsen salmijärvi, T lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>749687.2159774679</v>
+        <v>749671</v>
       </c>
       <c r="R39" t="n">
-        <v>7538152.057944613</v>
+        <v>7538144</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4953,22 +4392,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4977,13 +4406,14 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -4995,15 +4425,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>110047489</v>
+        <v>80979840</v>
       </c>
       <c r="B40" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5011,21 +4436,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5035,10 +4460,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>749816.9234223666</v>
+        <v>749766</v>
       </c>
       <c r="R40" t="n">
-        <v>7538237.456334162</v>
+        <v>7538212</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5065,22 +4490,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5095,7 +4510,7 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -5107,37 +4522,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>110047497</v>
+        <v>80979841</v>
       </c>
       <c r="B41" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5147,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>749807.801174833</v>
+        <v>749846</v>
       </c>
       <c r="R41" t="n">
-        <v>7538233.539382952</v>
+        <v>7538305</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5177,22 +4587,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5207,7 +4607,7 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -5219,15 +4619,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>110047491</v>
+        <v>80979842</v>
       </c>
       <c r="B42" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5259,10 +4654,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>749804.775457286</v>
+        <v>749797</v>
       </c>
       <c r="R42" t="n">
-        <v>7538229.451174593</v>
+        <v>7538317</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5289,22 +4684,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5319,7 +4704,7 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5331,37 +4716,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>110050051</v>
+        <v>80979843</v>
       </c>
       <c r="B43" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>232140</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,10 +4751,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>749719.4614537557</v>
+        <v>749679</v>
       </c>
       <c r="R43" t="n">
-        <v>7538180.223133828</v>
+        <v>7537999</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5401,22 +4781,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5431,7 +4801,7 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -5443,37 +4813,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>110047495</v>
+        <v>80979857</v>
       </c>
       <c r="B44" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5483,10 +4848,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>749818.9873157886</v>
+        <v>749680</v>
       </c>
       <c r="R44" t="n">
-        <v>7538235.757213106</v>
+        <v>7538022</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5513,22 +4878,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5543,7 +4898,7 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -5555,15 +4910,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>110050046</v>
+        <v>80979858</v>
       </c>
       <c r="B45" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5571,21 +4921,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5595,10 +4945,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>749732.6391948935</v>
+        <v>749718</v>
       </c>
       <c r="R45" t="n">
-        <v>7538181.493667146</v>
+        <v>7538171</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5625,22 +4975,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5655,7 +4995,7 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -5667,15 +5007,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>110047477</v>
+        <v>80979859</v>
       </c>
       <c r="B46" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5707,10 +5042,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>749853.8156241401</v>
+        <v>749840</v>
       </c>
       <c r="R46" t="n">
-        <v>7538229.246132255</v>
+        <v>7538311</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5737,22 +5072,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5767,7 +5092,7 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -5779,15 +5104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>110047471</v>
+        <v>80979860</v>
       </c>
       <c r="B47" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5819,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>749830.1972224362</v>
+        <v>749666</v>
       </c>
       <c r="R47" t="n">
-        <v>7538296.820639784</v>
+        <v>7538151</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5849,22 +5169,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5879,7 +5189,7 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -5891,15 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>110047472</v>
+        <v>80979861</v>
       </c>
       <c r="B48" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5931,10 +5236,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>749858.5469831147</v>
+        <v>749644</v>
       </c>
       <c r="R48" t="n">
-        <v>7538247.165943973</v>
+        <v>7538111</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5961,22 +5266,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5991,7 +5286,7 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -6003,15 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>110050030</v>
+        <v>80979862</v>
       </c>
       <c r="B49" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6043,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>749715.582271572</v>
+        <v>749848</v>
       </c>
       <c r="R49" t="n">
-        <v>7538169.219110462</v>
+        <v>7538304</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6073,22 +5363,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6103,7 +5383,7 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -6115,15 +5395,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>110047486</v>
+        <v>80979863</v>
       </c>
       <c r="B50" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6155,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>749792.5059387208</v>
+        <v>749697</v>
       </c>
       <c r="R50" t="n">
-        <v>7538250.286772298</v>
+        <v>7538148</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6185,22 +5460,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6215,7 +5480,7 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -6227,37 +5492,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>110047498</v>
+        <v>80979864</v>
       </c>
       <c r="B51" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6267,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>749782.7395398659</v>
+        <v>749734</v>
       </c>
       <c r="R51" t="n">
-        <v>7538245.168893935</v>
+        <v>7538208</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6297,22 +5557,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6327,7 +5577,7 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -6339,37 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>110050034</v>
+        <v>91819291</v>
       </c>
       <c r="B52" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6379,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>749719.4614537557</v>
+        <v>749675</v>
       </c>
       <c r="R52" t="n">
-        <v>7538180.223133828</v>
+        <v>7538023</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6409,22 +5654,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6439,7 +5674,7 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -6451,37 +5686,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>110050048</v>
+        <v>91819294</v>
       </c>
       <c r="B53" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6491,10 +5721,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>749711.680657233</v>
+        <v>749762</v>
       </c>
       <c r="R53" t="n">
-        <v>7538162.388993432</v>
+        <v>7538235</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6521,22 +5751,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6551,7 +5771,7 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -6563,15 +5783,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>110050035</v>
+        <v>91819299</v>
       </c>
       <c r="B54" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6579,21 +5794,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6603,10 +5818,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>749723.6168781928</v>
+        <v>749687</v>
       </c>
       <c r="R54" t="n">
-        <v>7538184.420200526</v>
+        <v>7538152</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6633,22 +5848,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6663,7 +5868,7 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -6675,15 +5880,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>110047499</v>
+        <v>110047471</v>
       </c>
       <c r="B55" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6715,10 +5915,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>749779.7050400365</v>
+        <v>749830</v>
       </c>
       <c r="R55" t="n">
-        <v>7538249.052237583</v>
+        <v>7538297</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6748,19 +5948,9 @@
           <t>2022-08-26</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6787,10 +5977,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128691463</v>
+        <v>110047472</v>
       </c>
       <c r="B56" t="n">
-        <v>92820</v>
+        <v>93191</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6818,14 +6008,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Saarijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>749698</v>
+        <v>749859</v>
       </c>
       <c r="R56" t="n">
-        <v>7538155</v>
+        <v>7538247</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6852,12 +6042,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6872,22 +6062,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128691423</v>
+        <v>110047474</v>
       </c>
       <c r="B57" t="n">
-        <v>91454</v>
+        <v>93191</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6895,34 +6085,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Saarijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>749677</v>
+        <v>749840</v>
       </c>
       <c r="R57" t="n">
-        <v>7538134</v>
+        <v>7538308</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6949,12 +6139,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6969,57 +6159,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128691457</v>
+        <v>110047477</v>
       </c>
       <c r="B58" t="n">
-        <v>92826</v>
+        <v>93191</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Saarijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>749701</v>
+        <v>749854</v>
       </c>
       <c r="R58" t="n">
-        <v>7538166</v>
+        <v>7538229</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7046,12 +6236,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7066,22 +6256,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128691459</v>
+        <v>110047486</v>
       </c>
       <c r="B59" t="n">
-        <v>92820</v>
+        <v>93191</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7109,14 +6299,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Saarijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>749749</v>
+        <v>749792</v>
       </c>
       <c r="R59" t="n">
-        <v>7538214</v>
+        <v>7538250</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7143,12 +6333,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7163,22 +6353,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128691440</v>
+        <v>110047491</v>
       </c>
       <c r="B60" t="n">
-        <v>92864</v>
+        <v>93191</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7186,34 +6376,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Saarijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749833</v>
+        <v>749805</v>
       </c>
       <c r="R60" t="n">
-        <v>7538296</v>
+        <v>7538229</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7240,12 +6430,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7260,57 +6450,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128691455</v>
+        <v>110047499</v>
       </c>
       <c r="B61" t="n">
-        <v>91794</v>
+        <v>93191</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>65</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Saarijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>749707</v>
+        <v>749780</v>
       </c>
       <c r="R61" t="n">
-        <v>7538174</v>
+        <v>7538249</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7337,12 +6527,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7357,22 +6547,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128691422</v>
+        <v>110050030</v>
       </c>
       <c r="B62" t="n">
-        <v>91454</v>
+        <v>93191</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7380,34 +6570,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Saarijärvi, T lm</t>
+          <t>Esrangeåsen, T lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>749652</v>
+        <v>749716</v>
       </c>
       <c r="R62" t="n">
-        <v>7538048</v>
+        <v>7538169</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7434,12 +6624,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7454,44 +6644,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128691456</v>
+        <v>128691459</v>
       </c>
       <c r="B63" t="n">
-        <v>92826</v>
+        <v>93191</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7501,10 +6691,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>749799</v>
+        <v>749749</v>
       </c>
       <c r="R63" t="n">
-        <v>7538192</v>
+        <v>7538214</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7563,10 +6753,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128691462</v>
+        <v>128691461</v>
       </c>
       <c r="B64" t="n">
-        <v>92820</v>
+        <v>93191</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7598,10 +6788,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>749676</v>
+        <v>749702</v>
       </c>
       <c r="R64" t="n">
-        <v>7538135</v>
+        <v>7538089</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7660,10 +6850,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128691425</v>
+        <v>128691462</v>
       </c>
       <c r="B65" t="n">
-        <v>79658</v>
+        <v>93191</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7671,21 +6861,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7695,10 +6885,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>749710</v>
+        <v>749676</v>
       </c>
       <c r="R65" t="n">
-        <v>7538102</v>
+        <v>7538135</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7757,10 +6947,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128691438</v>
+        <v>128691463</v>
       </c>
       <c r="B66" t="n">
-        <v>92818</v>
+        <v>93191</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7768,21 +6958,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7792,10 +6982,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>749709</v>
+        <v>749698</v>
       </c>
       <c r="R66" t="n">
-        <v>7538091</v>
+        <v>7538155</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7854,10 +7044,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128691461</v>
+        <v>79931213</v>
       </c>
       <c r="B67" t="n">
-        <v>92820</v>
+        <v>93197</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7865,34 +7055,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Saarijärvi, T lm</t>
+          <t>Esrangeåsen salmijärvi, T lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>749702</v>
+        <v>749687</v>
       </c>
       <c r="R67" t="n">
-        <v>7538089</v>
+        <v>7538163</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7919,12 +7112,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7933,21 +7126,1687 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>79931285</v>
+      </c>
+      <c r="B68" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Esrangeåsen salmijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>749695</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7538151</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>80979855</v>
+      </c>
+      <c r="B69" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Esrangeåsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>749692</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7538147</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>80979856</v>
+      </c>
+      <c r="B70" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Esrangeåsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>749685</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7538159</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128691456</v>
+      </c>
+      <c r="B71" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>749799</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7538192</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
           <t>Christina Boyd</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
+      <c r="AX71" t="inlineStr">
         <is>
           <t>Christina Boyd</t>
         </is>
       </c>
-      <c r="AY67" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128691457</v>
+      </c>
+      <c r="B72" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>749701</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7538166</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>79931237</v>
+      </c>
+      <c r="B73" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Esrangeåsen salmijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>749720</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7538177</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>80979850</v>
+      </c>
+      <c r="B74" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Esrangeåsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>749718</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7538183</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>110050034</v>
+      </c>
+      <c r="B75" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Esrangeåsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>749720</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7538180</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>79931308</v>
+      </c>
+      <c r="B76" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Esrangeåsen salmijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>749723</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7538187</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>80979849</v>
+      </c>
+      <c r="B77" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Esrangeåsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>749718</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7538184</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128691440</v>
+      </c>
+      <c r="B78" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>749833</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7538296</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>110047497</v>
+      </c>
+      <c r="B79" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Esrangeåsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>749808</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7538233</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2022-08-26</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2022-08-26</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>110047498</v>
+      </c>
+      <c r="B80" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Esrangeåsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>749783</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7538245</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2022-08-26</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2022-08-26</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128691425</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Saarijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>749710</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7538102</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>79931364</v>
+      </c>
+      <c r="B82" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Esrangeåsen salmijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>749738</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7538209</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>80979852</v>
+      </c>
+      <c r="B83" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Esrangeåsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>749698</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7538114</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>110050051</v>
+      </c>
+      <c r="B84" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Esrangeåsen, T lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>749720</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7538180</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79797228</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979854</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050048</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691455</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931103</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931201</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979847</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979848</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91819293</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,6 +1704,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91819301</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1751,6 +1806,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047495</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1852,6 +1912,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931255</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1949,6 +2014,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979853</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2046,6 +2116,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050035</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931067</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979851</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91819292</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91819295</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2539,6 +2634,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931048</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2640,6 +2740,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931078</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2741,6 +2846,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931208</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2838,6 +2948,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979844</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2935,6 +3050,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979845</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3032,6 +3152,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979846</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3129,6 +3254,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91819298</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3226,6 +3356,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691422</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3323,6 +3458,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691423</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3420,6 +3560,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047489</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3517,6 +3662,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050046</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3614,6 +3764,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691438</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3715,6 +3870,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79797210</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3816,6 +3976,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79930988</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3917,6 +4082,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79930997</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4018,6 +4188,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931166</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4119,6 +4294,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931186</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4220,6 +4400,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931265</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4321,6 +4506,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931274</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4422,6 +4612,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931292</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4519,6 +4714,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979840</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4616,6 +4816,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979841</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4713,6 +4918,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979842</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4810,6 +5020,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979843</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4907,6 +5122,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979857</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5004,6 +5224,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979858</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5101,6 +5326,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979859</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5198,6 +5428,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979860</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5295,6 +5530,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979861</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5392,6 +5632,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979862</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5489,6 +5734,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979863</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5586,6 +5836,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979864</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5683,6 +5938,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91819291</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5780,6 +6040,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91819294</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5877,6 +6142,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91819299</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5974,6 +6244,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047471</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6071,6 +6346,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047472</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6168,6 +6448,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047474</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6265,6 +6550,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047477</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6362,6 +6652,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047486</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6459,6 +6754,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047491</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6556,6 +6856,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047499</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6653,6 +6958,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050030</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6750,6 +7060,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691459</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6847,6 +7162,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691461</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6944,6 +7264,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691462</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7041,6 +7366,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691463</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7142,6 +7472,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931213</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7243,6 +7578,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931285</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7340,6 +7680,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979855</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7437,6 +7782,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979856</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7534,6 +7884,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691456</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7631,6 +7986,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691457</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7732,6 +8092,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931237</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7829,6 +8194,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979850</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7926,6 +8296,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050034</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8027,6 +8402,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931308</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8124,6 +8504,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979849</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8221,6 +8606,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691440</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8318,6 +8708,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047497</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8415,6 +8810,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047498</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8512,6 +8912,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691425</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8613,6 +9018,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79931364</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8710,6 +9120,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80979852</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8807,8 +9222,98 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050051</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>